--- a/validation/sds4_analysis.xlsx
+++ b/validation/sds4_analysis.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chart_Imr" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Chart_R" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Full_Dataset" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Visual_Charts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart_XmR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Residuals" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effects" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interactions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual_Charts" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -147,7 +148,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -162,38 +163,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="3171825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -494,7 +470,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -528,7 +504,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Single condition over time (K=1)</t>
+          <t>No replication (all cells n=1)</t>
         </is>
       </c>
     </row>
@@ -551,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>single_stream</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -579,7 +555,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Imr</t>
+          <t>XmR</t>
         </is>
       </c>
     </row>
@@ -603,7 +579,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>('factor 1',)</t>
         </is>
       </c>
     </row>
@@ -652,7 +628,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -663,7 +639,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Imr, R</t>
+          <t>XmR</t>
         </is>
       </c>
     </row>
@@ -700,7 +676,7 @@
         </is>
       </c>
       <c r="B20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -710,7 +686,7 @@
         </is>
       </c>
       <c r="B21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -720,7 +696,7 @@
         </is>
       </c>
       <c r="B22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -739,8 +715,10 @@
           <t>Interaction Analysis</t>
         </is>
       </c>
-      <c r="B24" t="b">
-        <v>0</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -766,7 +744,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -789,7 +767,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>time_series</t>
+          <t>all_residuals</t>
         </is>
       </c>
     </row>
@@ -797,7 +775,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>imr_chart</t>
+          <t>limited_interactions</t>
         </is>
       </c>
     </row>
@@ -805,7 +783,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>trend_analysis</t>
+          <t>main_effects</t>
         </is>
       </c>
     </row>
@@ -820,16 +798,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -840,30 +819,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>rsg</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>center</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>lpl</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>upl</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>beyond_limits</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>obs_id</t>
         </is>
@@ -873,22 +857,27 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>50.343</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>49.964</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>49.11</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>50.817</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -896,22 +885,27 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>50.107</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>49.964</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>49.11</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>50.817</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -919,22 +913,27 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>49.736</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>49.964</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>49.11</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>50.817</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -942,22 +941,27 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>50.236</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>49.964</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>49.11</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>50.817</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -965,22 +969,27 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>49.897</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>49.964</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>49.11</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>50.817</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>4</v>
       </c>
     </row>
@@ -988,22 +997,27 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>49.743</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>49.964</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>49.11</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>50.817</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1011,22 +1025,27 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>50.023</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>49.964</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>49.11</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>50.817</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1034,22 +1053,27 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>49.717</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>49.964</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>49.11</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>50.817</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1057,22 +1081,27 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>49.896</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>49.964</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>49.11</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>50.817</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1080,22 +1109,27 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>49.524</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>49.964</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>49.11</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>50.817</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1103,22 +1137,27 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>49.744</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>49.964</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>49.11</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>50.817</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1126,22 +1165,27 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>49.998</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>49.964</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>49.11</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>50.817</v>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1149,22 +1193,27 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>49.172</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>49.964</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>49.11</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>50.817</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1172,22 +1221,27 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>49.796</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>49.964</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>49.11</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>50.817</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1195,22 +1249,27 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>49.806</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>49.964</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>49.11</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>50.817</v>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1218,22 +1277,27 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>49.61</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>49.964</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>49.11</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>50.817</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1241,22 +1305,27 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>49.811</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>49.964</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>49.11</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>50.817</v>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1264,22 +1333,27 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>50.375</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>49.964</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>49.11</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>50.817</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1287,22 +1361,27 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>49.562</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>49.964</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>49.11</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>50.817</v>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1310,22 +1389,27 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>50.289</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>49.964</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>49.11</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>50.817</v>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1333,22 +1417,27 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>49.2</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>49.964</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>49.11</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>50.817</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1356,22 +1445,27 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
         <v>49.637</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>49.964</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>49.11</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>50.817</v>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
       <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1379,22 +1473,27 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>50.02</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>49.964</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>49.11</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>50.817</v>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1402,22 +1501,27 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>50.166</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>49.964</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>49.11</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>50.817</v>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1425,22 +1529,27 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
         <v>50.152</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>49.964</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>49.11</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>50.817</v>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
       <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1448,22 +1557,27 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
         <v>50.132</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>49.964</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>49.11</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>50.817</v>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
       <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1471,22 +1585,27 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>49.755</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>49.964</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>49.11</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>50.817</v>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1494,22 +1613,27 @@
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
         <v>49.764</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>49.964</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>49.11</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>50.817</v>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1517,22 +1641,27 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>50.354</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>49.964</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>49.11</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>50.817</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
         <v>28</v>
       </c>
     </row>
@@ -1540,22 +1669,27 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>49.999</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>49.964</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>49.11</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>50.817</v>
       </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
       <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
         <v>29</v>
       </c>
     </row>
@@ -1563,22 +1697,27 @@
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
         <v>49.887</v>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>49.964</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>49.11</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>50.817</v>
       </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1586,22 +1725,27 @@
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
         <v>49.883</v>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>49.964</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>49.11</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>50.817</v>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
       <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
         <v>31</v>
       </c>
     </row>
@@ -1609,22 +1753,27 @@
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
         <v>49.891</v>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>49.964</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>49.11</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>50.817</v>
       </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
       <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
         <v>32</v>
       </c>
     </row>
@@ -1632,22 +1781,27 @@
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
         <v>50.336</v>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>49.964</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
         <v>49.11</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>50.817</v>
       </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
       <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
         <v>33</v>
       </c>
     </row>
@@ -1655,22 +1809,27 @@
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
         <v>50.286</v>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>49.964</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>49.11</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>50.817</v>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
       <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
         <v>34</v>
       </c>
     </row>
@@ -1678,22 +1837,27 @@
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>50.675</v>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>49.964</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>49.11</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>50.817</v>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
       <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
         <v>35</v>
       </c>
     </row>
@@ -1701,22 +1865,27 @@
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
         <v>50.211</v>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>49.964</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>49.11</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>50.817</v>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
       <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
         <v>36</v>
       </c>
     </row>
@@ -1724,22 +1893,27 @@
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
         <v>50.319</v>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>49.964</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
         <v>49.11</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>50.817</v>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
       <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
         <v>37</v>
       </c>
     </row>
@@ -1747,22 +1921,27 @@
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
         <v>50.382</v>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>49.964</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
         <v>49.11</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>50.817</v>
       </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
       <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
         <v>38</v>
       </c>
     </row>
@@ -1770,22 +1949,27 @@
       <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
         <v>50.106</v>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>49.964</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
         <v>49.11</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>50.817</v>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
       <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
         <v>39</v>
       </c>
     </row>
@@ -1800,16 +1984,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1820,930 +2005,1158 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>mr</t>
+          <t>factor 1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>y</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>lpl</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>upl</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>beyond_limits</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>obs_id</t>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>R5</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.236</v>
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>0.321</v>
+        <v>50.34300923044454</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.3794954353429816</v>
       </c>
       <c r="E2" t="n">
-        <v>1.048</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.3794954353429816</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.371</v>
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>0.321</v>
+        <v>50.10697165334917</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.1434578582476149</v>
       </c>
       <c r="E3" t="n">
-        <v>1.048</v>
+        <v>-0.1180187885476833</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0.02543906969993159</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.1180187885476833</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.5</v>
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>0.321</v>
+        <v>49.73607374248258</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0.2274400526189737</v>
       </c>
       <c r="E4" t="n">
-        <v>1.048</v>
+        <v>-0.1854489554332943</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>-0.412889008052268</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.1854489554332943</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.339</v>
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>0.321</v>
+        <v>50.23622686208343</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.272713066981872</v>
       </c>
       <c r="E5" t="n">
-        <v>1.048</v>
+        <v>0.2500765598004229</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>0.5227896267822949</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2500765598004229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.155</v>
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>0.321</v>
+        <v>49.89738137821496</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0.06613241688659599</v>
       </c>
       <c r="E6" t="n">
-        <v>1.048</v>
+        <v>-0.169422741934234</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>-0.23555515882083</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.169422741934234</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.28</v>
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>0.321</v>
+        <v>49.74285556722092</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.2206582278806337</v>
       </c>
       <c r="E7" t="n">
-        <v>1.048</v>
+        <v>-0.07726290549701886</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>-0.2979211333776526</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.07726290549701886</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.307</v>
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>0.321</v>
+        <v>50.02312770018369</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.05961390508213071</v>
       </c>
       <c r="E8" t="n">
-        <v>1.048</v>
+        <v>0.1401360664813822</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>0.1997499715635129</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1401360664813822</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.18</v>
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>0.321</v>
+        <v>49.71655801966275</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.2469557754388063</v>
       </c>
       <c r="E9" t="n">
-        <v>1.048</v>
+        <v>-0.1532848402604685</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>-0.4002406156992748</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.1532848402604685</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.372</v>
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>0.321</v>
+        <v>49.89616505175599</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.06734874334556196</v>
       </c>
       <c r="E10" t="n">
-        <v>1.048</v>
+        <v>0.08980351604662218</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>0.02245477270106022</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.08980351604662218</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.221</v>
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C11" t="n">
-        <v>0.321</v>
+        <v>49.52367466518675</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.4398391299148017</v>
       </c>
       <c r="E11" t="n">
-        <v>1.048</v>
+        <v>-0.1862451932846199</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>-0.6260843231994215</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.1862451932846199</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.254</v>
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C12" t="n">
-        <v>0.321</v>
+        <v>49.74420049309661</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.2193133020049487</v>
       </c>
       <c r="E12" t="n">
-        <v>1.048</v>
+        <v>0.1102629139549265</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>11</v>
+        <v>-0.1090503880500222</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1102629139549265</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.825</v>
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C13" t="n">
-        <v>0.321</v>
+        <v>49.99773681427038</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.0342230191688202</v>
       </c>
       <c r="E13" t="n">
-        <v>1.048</v>
+        <v>0.1267681605868844</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>0.1609911797557046</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1267681605868844</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.624</v>
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C14" t="n">
-        <v>0.321</v>
+        <v>49.17226380062688</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0.7912499944746756</v>
       </c>
       <c r="E14" t="n">
-        <v>1.048</v>
+        <v>-0.4127365068217479</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>-1.203986501296423</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.4127365068217479</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.01</v>
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C15" t="n">
-        <v>0.321</v>
+        <v>49.79634382307143</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0.1671699720301234</v>
       </c>
       <c r="E15" t="n">
-        <v>1.048</v>
+        <v>0.3120400112222761</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>14</v>
+        <v>0.1448700391921527</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3120400112222761</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0.196</v>
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C16" t="n">
-        <v>0.321</v>
+        <v>49.80618964923504</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0.157324145866518</v>
       </c>
       <c r="E16" t="n">
-        <v>1.048</v>
+        <v>0.004922913081802704</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>15</v>
+        <v>-0.1524012327847153</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.004922913081802704</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.201</v>
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C17" t="n">
-        <v>0.321</v>
+        <v>49.60989370222233</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0.3536200928792255</v>
       </c>
       <c r="E17" t="n">
-        <v>1.048</v>
+        <v>-0.09814797350635374</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>16</v>
+        <v>-0.4517680663855792</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.09814797350635374</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>18</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.5639999999999999</v>
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C18" t="n">
-        <v>0.321</v>
+        <v>49.81070055864136</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0.1528132364601902</v>
       </c>
       <c r="E18" t="n">
-        <v>1.048</v>
+        <v>0.1004034282095176</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>17</v>
+        <v>-0.05240980825067254</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1004034282095176</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>19</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.8129999999999999</v>
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C19" t="n">
-        <v>0.321</v>
+        <v>50.37490159350146</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.4113877983999004</v>
       </c>
       <c r="E19" t="n">
-        <v>1.048</v>
+        <v>0.2821005174300453</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>18</v>
+        <v>0.6934883158299456</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2821005174300453</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.726</v>
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C20" t="n">
-        <v>0.321</v>
+        <v>49.56236016792649</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-0.4011536271750629</v>
       </c>
       <c r="E20" t="n">
-        <v>1.048</v>
+        <v>-0.4062707127874816</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>19</v>
+        <v>-0.8074243399625445</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.4062707127874816</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21</v>
-      </c>
-      <c r="B21" t="n">
-        <v>1.088</v>
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C21" t="n">
-        <v>0.321</v>
+        <v>50.28851506939244</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.3250012742908837</v>
       </c>
       <c r="E21" t="n">
-        <v>1.048</v>
+        <v>0.3630774507329733</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>0.6880787250238569</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3630774507329733</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.437</v>
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C22" t="n">
-        <v>0.321</v>
+        <v>49.20032646437774</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-0.7631873307238166</v>
       </c>
       <c r="E22" t="n">
-        <v>1.048</v>
+        <v>-0.5440943025073501</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>21</v>
+        <v>-1.307281633231167</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.5440943025073501</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>23</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.382</v>
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C23" t="n">
-        <v>0.321</v>
+        <v>49.63738092936915</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-0.3261328657324043</v>
       </c>
       <c r="E23" t="n">
-        <v>1.048</v>
+        <v>0.2185272324957062</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>22</v>
+        <v>-0.1076056332366981</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2185272324957062</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0.146</v>
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C24" t="n">
-        <v>0.321</v>
+        <v>50.01981736820657</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.05630357310501921</v>
       </c>
       <c r="E24" t="n">
-        <v>1.048</v>
+        <v>0.1912182194187118</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>23</v>
+        <v>0.247521792523731</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1912182194187118</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.014</v>
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C25" t="n">
-        <v>0.321</v>
+        <v>50.16602565239796</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.2025118572964075</v>
       </c>
       <c r="E25" t="n">
-        <v>1.048</v>
+        <v>0.07310414209569416</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>24</v>
+        <v>0.2756159993921017</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.07310414209569416</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0.02</v>
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C26" t="n">
-        <v>0.321</v>
+        <v>50.15177817844692</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.1882643833453699</v>
       </c>
       <c r="E26" t="n">
-        <v>1.048</v>
+        <v>-0.007123736975518824</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>25</v>
+        <v>0.1811406463698511</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.007123736975518824</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0.377</v>
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C27" t="n">
-        <v>0.321</v>
+        <v>50.13180640803652</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.1682926129349624</v>
       </c>
       <c r="E27" t="n">
-        <v>1.048</v>
+        <v>-0.009985885205203715</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>26</v>
+        <v>0.1583067277297587</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.009985885205203715</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0.008999999999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C28" t="n">
-        <v>0.321</v>
+        <v>49.75482386289018</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>-0.208689932211378</v>
       </c>
       <c r="E28" t="n">
-        <v>1.048</v>
+        <v>-0.1884912725731702</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>27</v>
+        <v>-0.3971812047845482</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.1884912725731702</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>29</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0.59</v>
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C29" t="n">
-        <v>0.321</v>
+        <v>49.76418978437834</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-0.1993240107232168</v>
       </c>
       <c r="E29" t="n">
-        <v>1.048</v>
+        <v>0.004682960744080589</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>28</v>
+        <v>-0.1946410499791362</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.004682960744080589</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0.355</v>
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C30" t="n">
-        <v>0.321</v>
+        <v>50.35423074568642</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.3907169505848671</v>
       </c>
       <c r="E30" t="n">
-        <v>1.048</v>
+        <v>0.295020480654042</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>29</v>
+        <v>0.6857374312389091</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.295020480654042</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0.113</v>
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C31" t="n">
-        <v>0.321</v>
+        <v>49.9991418136821</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.03562801858054598</v>
       </c>
       <c r="E31" t="n">
-        <v>1.048</v>
+        <v>-0.1775444660021606</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>30</v>
+        <v>-0.1419164474216146</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.1775444660021606</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>32</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0.004</v>
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C32" t="n">
-        <v>0.321</v>
+        <v>49.88663615443014</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>-0.07687764067141245</v>
       </c>
       <c r="E32" t="n">
-        <v>1.048</v>
+        <v>-0.05625282962597922</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>31</v>
+        <v>-0.1331304702973917</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.05625282962597922</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>33</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0.008999999999999999</v>
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C33" t="n">
-        <v>0.321</v>
+        <v>49.88263354570623</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>-0.08088024939532801</v>
       </c>
       <c r="E33" t="n">
-        <v>1.048</v>
+        <v>-0.002001304361957779</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>32</v>
+        <v>-0.08288155375728579</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.002001304361957779</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>34</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0.445</v>
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C34" t="n">
-        <v>0.321</v>
+        <v>49.89133110754624</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>-0.07218268755531199</v>
       </c>
       <c r="E34" t="n">
-        <v>1.048</v>
+        <v>0.004348780920008011</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>33</v>
+        <v>-0.06783390663530398</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.004348780920008011</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>35</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0.049</v>
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C35" t="n">
-        <v>0.321</v>
+        <v>50.33591041033122</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.3723966152296612</v>
       </c>
       <c r="E35" t="n">
-        <v>1.048</v>
+        <v>0.2222896513924866</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>34</v>
+        <v>0.5946862666221477</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2222896513924866</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>36</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0.389</v>
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C36" t="n">
-        <v>0.321</v>
+        <v>50.28641332052426</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.3228995254227058</v>
       </c>
       <c r="E36" t="n">
-        <v>1.048</v>
+        <v>-0.02474854490347767</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>35</v>
+        <v>0.2981509805192282</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.02474854490347767</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>37</v>
-      </c>
-      <c r="B37" t="n">
-        <v>0.464</v>
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C37" t="n">
-        <v>0.321</v>
+        <v>50.67498301163128</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>0.7114692165297214</v>
       </c>
       <c r="E37" t="n">
-        <v>1.048</v>
+        <v>0.1942848455535078</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>36</v>
+        <v>0.9057540620832292</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1942848455535078</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>38</v>
-      </c>
-      <c r="B38" t="n">
-        <v>0.108</v>
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C38" t="n">
-        <v>0.321</v>
+        <v>50.21079569282132</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.2472818977197662</v>
       </c>
       <c r="E38" t="n">
-        <v>1.048</v>
+        <v>-0.2320936594049776</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>37</v>
+        <v>0.01518823831478855</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.2320936594049776</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>39</v>
-      </c>
-      <c r="B39" t="n">
-        <v>0.063</v>
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
       </c>
       <c r="C39" t="n">
-        <v>0.321</v>
+        <v>50.31908915624224</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>0.3555753611406871</v>
       </c>
       <c r="E39" t="n">
-        <v>1.048</v>
+        <v>0.05414673171046047</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>38</v>
+        <v>0.4097220928511476</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.05414673171046047</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>50.38223725504481</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.4187234599432514</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.03157404940128217</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.4502975093445336</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.03157404940128217</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B40" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1.048</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>39</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>50.10585139974348</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.1423376046419236</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.1381929276506639</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.004144676991259644</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-0.1381929276506639</v>
       </c>
     </row>
   </sheetData>
@@ -2757,881 +3170,1259 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Effect_Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>factor 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.002964472883763225</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>main_effect</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.002964472883763225</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>time</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>obs_id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>rsg_key</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>cell_key</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>50.34300923044454</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>(1,)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>50.10697165334917</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>(2,)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>49.73607374248258</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>(3,)</t>
-        </is>
+        <v>0.3794954353429816</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>50.23622686208343</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(4,)</t>
-        </is>
+        <v>0.1434578582476149</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>49.89738137821496</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>(5,)</t>
-        </is>
+        <v>-0.2274400526189737</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>49.74285556722092</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>(6,)</t>
-        </is>
+        <v>0.272713066981872</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>50.02312770018369</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>(7,)</t>
-        </is>
+        <v>-0.06613241688659599</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>49.71655801966275</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>(8,)</t>
-        </is>
+        <v>-0.2206582278806337</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>49.89616505175599</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>(9,)</t>
-        </is>
+        <v>0.05961390508213071</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>49.52367466518675</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>(10,)</t>
-        </is>
+        <v>-0.2469557754388063</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>49.74420049309661</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>(11,)</t>
-        </is>
+        <v>-0.06734874334556196</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>49.99773681427038</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>(12,)</t>
-        </is>
+        <v>-0.4398391299148017</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>49.17226380062688</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>(13,)</t>
-        </is>
+        <v>-0.2193133020049487</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="n">
-        <v>49.79634382307142</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>(14,)</t>
-        </is>
+        <v>0.0342230191688202</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>49.80618964923504</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>(15,)</t>
-        </is>
+        <v>-0.7912499944746756</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="n">
-        <v>49.60989370222233</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>(16,)</t>
-        </is>
+        <v>-0.1671699720301234</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="n">
-        <v>49.81070055864136</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>(17,)</t>
-        </is>
+        <v>-0.157324145866518</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="n">
-        <v>50.37490159350146</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>(18,)</t>
-        </is>
+        <v>-0.3536200928792255</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="n">
-        <v>49.56236016792649</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>(19,)</t>
-        </is>
+        <v>-0.1528132364601902</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="n">
-        <v>50.28851506939244</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>(20,)</t>
-        </is>
+        <v>0.4113877983999004</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="n">
-        <v>49.20032646437774</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>(21,)</t>
-        </is>
+        <v>-0.4011536271750629</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="n">
-        <v>49.63738092936915</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
       </c>
       <c r="C23" t="n">
-        <v>21</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>(22,)</t>
-        </is>
+        <v>0.3250012742908837</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="n">
-        <v>50.01981736820657</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>(23,)</t>
-        </is>
+        <v>-0.7631873307238166</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="n">
-        <v>50.16602565239796</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
       </c>
       <c r="C25" t="n">
-        <v>23</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>(24,)</t>
-        </is>
+        <v>-0.3261328657324043</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="n">
-        <v>50.15177817844692</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>(25,)</t>
-        </is>
+        <v>0.05630357310501921</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="n">
-        <v>50.13180640803652</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>(26,)</t>
-        </is>
+        <v>0.2025118572964075</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="n">
-        <v>49.75482386289018</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
       </c>
       <c r="C28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>(27,)</t>
-        </is>
+        <v>0.1882643833453699</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="n">
-        <v>49.76418978437834</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="C29" t="n">
-        <v>27</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>(28,)</t>
-        </is>
+        <v>0.1682926129349624</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="n">
-        <v>50.35423074568642</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
       </c>
       <c r="C30" t="n">
-        <v>28</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>(29,)</t>
-        </is>
+        <v>-0.208689932211378</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="n">
-        <v>49.9991418136821</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
       </c>
       <c r="C31" t="n">
-        <v>29</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>(30,)</t>
-        </is>
+        <v>-0.1993240107232168</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="n">
-        <v>49.88663615443014</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
       </c>
       <c r="C32" t="n">
-        <v>30</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>(31,)</t>
-        </is>
+        <v>0.3907169505848671</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="n">
-        <v>49.88263354570623</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
       </c>
       <c r="C33" t="n">
-        <v>31</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>(32,)</t>
-        </is>
+        <v>0.03562801858054598</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="n">
-        <v>49.89133110754624</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
       </c>
       <c r="C34" t="n">
-        <v>32</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>(33,)</t>
-        </is>
+        <v>-0.07687764067141245</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="n">
-        <v>50.33591041033122</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
       </c>
       <c r="C35" t="n">
-        <v>33</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>(34,)</t>
-        </is>
+        <v>-0.08088024939532801</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="n">
-        <v>50.28641332052426</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
       </c>
       <c r="C36" t="n">
-        <v>34</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>(35,)</t>
-        </is>
+        <v>-0.07218268755531199</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="n">
-        <v>50.67498301163128</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
       </c>
       <c r="C37" t="n">
-        <v>35</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>(36,)</t>
-        </is>
+        <v>0.3723966152296612</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="n">
-        <v>50.21079569282132</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
       </c>
       <c r="C38" t="n">
-        <v>36</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>(37,)</t>
-        </is>
+        <v>0.3228995254227058</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="n">
-        <v>50.31908915624224</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
       </c>
       <c r="C39" t="n">
-        <v>37</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>(38,)</t>
-        </is>
+        <v>0.7114692165297214</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="n">
-        <v>50.38223725504481</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
       </c>
       <c r="C40" t="n">
-        <v>38</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>(39,)</t>
-        </is>
+        <v>0.2472818977197662</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="n">
-        <v>50.10585139974348</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
       </c>
       <c r="C41" t="n">
-        <v>39</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>(40,)</t>
-        </is>
+        <v>0.3555753611406871</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.4187234599432514</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.1423376046419236</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.002964472883763225</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.1209832614314466</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.1884134283170575</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.2471120869166596</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.1723872148179972</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.08022737838078209</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.137171593597619</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.1562493131442317</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.08683904316285895</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.1892096661683831</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.1072984410711633</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.1238036877031212</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.4157009797055111</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.3090755383385129</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.001958440198039479</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.101112446390117</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.09743895532575442</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.279136044546282</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.4092351856712448</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.36011297784921</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.5470587753911134</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.2155627596119429</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.1882537465349485</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.07013966921193093</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.01008820985928205</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.01295035808896694</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.1914557454569334</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0.001718487860317364</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.2920560077702787</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.1805089388859238</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.05921730250974244</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.004965777245721004</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.001384308036244786</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.2193251785087234</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.02771301778724089</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.1913203726697446</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.2350581322887408</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0.05118225882669725</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0.02860957651751894</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>factor 1_MEs</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.1411574005344272</v>
       </c>
     </row>
   </sheetData>
@@ -3645,7 +4436,643 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Interaction</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Combination</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>factor_time</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3658,33 +5085,26 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Imr Chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>R Chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+          <t>XmR Chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>INTERACTIVE CHARTS</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Interactive HTML files have been exported alongside this Excel file.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Open the .html files in a web browser for full interactivity (zoom, pan, hover tooltips).</t>
         </is>
